--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484701_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484701_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>13.6727</v>
+        <v>13.3923</v>
       </c>
       <c r="E2" t="n">
-        <v>11.6529</v>
+        <v>11.5707</v>
       </c>
       <c r="F2" t="n">
-        <v>2.0197</v>
+        <v>1.8215</v>
       </c>
       <c r="G2" t="n">
         <v>5.5371</v>
@@ -610,13 +610,13 @@
         <v>2.0158</v>
       </c>
       <c r="S2" t="n">
-        <v>1.8294</v>
+        <v>1.549</v>
       </c>
       <c r="T2" t="n">
-        <v>1.2806</v>
+        <v>1.1984</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5488</v>
+        <v>0.3506</v>
       </c>
       <c r="V2" t="n">
         <v>5.3898</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>8.4801</v>
+        <v>9.508100000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>7.9727</v>
+        <v>8.852</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5074</v>
+        <v>0.6561</v>
       </c>
       <c r="G3" t="n">
         <v>8.273199999999999</v>
@@ -688,13 +688,13 @@
         <v>1.6493</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0078</v>
+        <v>1.0358</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0746</v>
+        <v>0.8047</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0825</v>
+        <v>0.2311</v>
       </c>
       <c r="V3" t="n">
         <v>-1.267</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. MATE SEBASTIA</t>
+          <t>K. MONTAÑO LINARES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.322</v>
+        <v>2.2256</v>
       </c>
       <c r="E4" t="n">
-        <v>1.9075</v>
+        <v>2.2256</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4145</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.1453</v>
+        <v>2.2256</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.1068</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0385</v>
+        <v>1.2502</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5735</v>
+        <v>2.2256</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5478</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0258</v>
+        <v>1.2502</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.7189</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.6546</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0643</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.4661</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3823</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>3.6244</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.8733</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0.751</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.6231</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.6231</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>K. MONTAÑO LINARES</t>
+          <t>J. MATE SEBASTIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2256</v>
+        <v>1.4784</v>
       </c>
       <c r="E5" t="n">
-        <v>2.2256</v>
+        <v>0.2869</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1.1916</v>
       </c>
       <c r="G5" t="n">
-        <v>2.2256</v>
+        <v>-1.1453</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9752999999999999</v>
+        <v>-1.1068</v>
       </c>
       <c r="I5" t="n">
-        <v>1.2502</v>
+        <v>-0.0385</v>
       </c>
       <c r="J5" t="n">
-        <v>2.2256</v>
+        <v>0.5735</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9752999999999999</v>
+        <v>0.5478</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2502</v>
+        <v>0.0258</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-1.7189</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-1.6546</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-0.0643</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.4661</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.3823</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.7807</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.2527</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>0.5281</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.6231</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-0.6231</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. TOKAEV TOKAEV</t>
+          <t>J. BALLESTER FERRANDIS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.0708</v>
+        <v>1.4646</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1664</v>
+        <v>0.3158</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2372</v>
+        <v>1.1489</v>
       </c>
       <c r="G6" t="n">
-        <v>0.093</v>
+        <v>0.4152</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.1956</v>
+        <v>-0.3957</v>
       </c>
       <c r="I6" t="n">
-        <v>2.2886</v>
+        <v>0.8109</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2733</v>
+        <v>0.1284</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.3103</v>
+        <v>0.0867</v>
       </c>
       <c r="L6" t="n">
-        <v>1.5836</v>
+        <v>0.0417</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1804</v>
+        <v>0.2869</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8854</v>
+        <v>-0.4824</v>
       </c>
       <c r="O6" t="n">
-        <v>0.705</v>
+        <v>0.7692</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.9163</v>
+        <v>0.5498</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.9321</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0158</v>
+        <v>0.5498</v>
       </c>
       <c r="S6" t="n">
-        <v>2.2502</v>
+        <v>0.4996</v>
       </c>
       <c r="T6" t="n">
-        <v>1.8484</v>
+        <v>0.1874</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4018</v>
+        <v>0.3122</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6439</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6439</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. BALLESTER FERRANDIS</t>
+          <t>D. TOKAEV TOKAEV</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.654</v>
+        <v>0.9661</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6042</v>
+        <v>-1.0729</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0498</v>
+        <v>2.039</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4152</v>
+        <v>0.093</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3957</v>
+        <v>-2.1956</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8109</v>
+        <v>2.2886</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1284</v>
+        <v>0.2733</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0867</v>
+        <v>-1.3103</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0417</v>
+        <v>1.5836</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2869</v>
+        <v>-0.1804</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4824</v>
+        <v>-0.8854</v>
       </c>
       <c r="O7" t="n">
-        <v>0.7692</v>
+        <v>0.705</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5498</v>
+        <v>-0.9163</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.9321</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5498</v>
+        <v>2.0158</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6889999999999999</v>
+        <v>1.1455</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4759</v>
+        <v>0.9419</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2131</v>
+        <v>0.2036</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.6439</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.6439</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. MARTIN MARGARIT</t>
+          <t>B. MONDRAGON VIDAL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3001</v>
+        <v>-0.5246</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8196</v>
+        <v>-2.2534</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5195</v>
+        <v>1.7288</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.0294</v>
+        <v>-2.0811</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.2537</v>
+        <v>0.2075</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2243</v>
+        <v>-2.2886</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.1211</v>
+        <v>-0.3133</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.1211</v>
+        <v>2.1674</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-2.4808</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9083</v>
+        <v>-1.7677</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.1326</v>
+        <v>-1.9599</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2243</v>
+        <v>0.1922</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3665</v>
+        <v>0.733</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9163</v>
+        <v>-2.0158</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2828</v>
+        <v>2.7489</v>
       </c>
       <c r="S9" t="n">
-        <v>1.6848</v>
+        <v>0.5119</v>
       </c>
       <c r="T9" t="n">
-        <v>1.2074</v>
+        <v>0.3873</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4774</v>
+        <v>0.1246</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3219</v>
+        <v>0.3115</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0104</v>
+        <v>-0.3115</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.3324</v>
+        <v>0.6231</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. PANOS HUERTAS</t>
+          <t>A. MARTIN MARGARIT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.7701</v>
+        <v>-0.5335</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1834</v>
+        <v>-1.053</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4133</v>
+        <v>0.5195</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.5156</v>
+        <v>-2.0294</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.6505</v>
+        <v>-2.2537</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1349</v>
+        <v>0.2243</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6713</v>
+        <v>-1.1211</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.7743</v>
+        <v>-1.1211</v>
       </c>
       <c r="L10" t="n">
-        <v>0.103</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.8443000000000001</v>
+        <v>-0.9083</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8762</v>
+        <v>-1.1326</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0318</v>
+        <v>0.2243</v>
       </c>
       <c r="P10" t="n">
-        <v>1.4661</v>
+        <v>0.3665</v>
       </c>
       <c r="Q10" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R10" t="n">
-        <v>2.3823</v>
+        <v>1.2828</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7755</v>
+        <v>1.4514</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9177999999999999</v>
+        <v>0.974</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1423</v>
+        <v>0.4774</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.945</v>
+        <v>-0.3219</v>
       </c>
       <c r="W10" t="n">
-        <v>0.3219</v>
+        <v>0.0104</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.267</v>
+        <v>-0.3324</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B. MONDRAGON VIDAL</t>
+          <t>M. PANOS HUERTAS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.1022</v>
+        <v>-0.6792</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.5585</v>
+        <v>-1.1668</v>
       </c>
       <c r="F11" t="n">
-        <v>1.4563</v>
+        <v>0.4876</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.0811</v>
+        <v>-1.5156</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2075</v>
+        <v>-1.6505</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.2886</v>
+        <v>0.1349</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.3133</v>
+        <v>-0.6713</v>
       </c>
       <c r="K11" t="n">
-        <v>2.1674</v>
+        <v>-0.7743</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.4808</v>
+        <v>0.103</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.7677</v>
+        <v>-0.8443000000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.9599</v>
+        <v>-0.8762</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1922</v>
+        <v>0.0318</v>
       </c>
       <c r="P11" t="n">
-        <v>0.733</v>
+        <v>1.4661</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.0158</v>
+        <v>-0.9163</v>
       </c>
       <c r="R11" t="n">
-        <v>2.7489</v>
+        <v>2.3823</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0657</v>
+        <v>0.3154</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9177999999999999</v>
+        <v>0.0988</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1479</v>
+        <v>0.2166</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3115</v>
+        <v>-0.945</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.3115</v>
+        <v>0.3219</v>
       </c>
       <c r="X11" t="n">
-        <v>0.6231</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.2418</v>
+        <v>-1.4775</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.0032</v>
+        <v>-1.4123</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2385</v>
+        <v>-0.06510000000000001</v>
       </c>
       <c r="G12" t="n">
         <v>-1.9358</v>
@@ -1390,13 +1390,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.306</v>
+        <v>0.4583</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1652</v>
+        <v>0.4257</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1408</v>
+        <v>0.0326</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.9007</v>
+        <v>-3.5879</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.1049</v>
+        <v>-2.569</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.7959000000000001</v>
+        <v>-1.0188</v>
       </c>
       <c r="G13" t="n">
         <v>-1.1118</v>
@@ -1468,13 +1468,13 @@
         <v>1.6493</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1109</v>
+        <v>0.2019</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4774</v>
+        <v>0.0585</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3664</v>
+        <v>0.1435</v>
       </c>
       <c r="V13" t="n">
         <v>-1.5785</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.905</v>
+        <v>-6.1052</v>
       </c>
       <c r="E14" t="n">
-        <v>-5.1669</v>
+        <v>-5.4414</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.7381</v>
+        <v>-0.6637999999999999</v>
       </c>
       <c r="G14" t="n">
         <v>-5.7328</v>
@@ -1546,13 +1546,13 @@
         <v>2.5656</v>
       </c>
       <c r="S14" t="n">
-        <v>2.3384</v>
+        <v>2.1382</v>
       </c>
       <c r="T14" t="n">
-        <v>1.994</v>
+        <v>1.7195</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3444</v>
+        <v>0.4187</v>
       </c>
       <c r="V14" t="n">
         <v>-0.3115</v>
@@ -1579,19 +1579,19 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>15.8555</v>
+        <v>16.7774</v>
       </c>
       <c r="E15" t="n">
-        <v>8.010199999999999</v>
+        <v>8.932399999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>7.845200000000001</v>
+        <v>7.8453</v>
       </c>
       <c r="G15" t="n">
         <v>1.642499999999998</v>
       </c>
       <c r="H15" t="n">
-        <v>-6.212000000000001</v>
+        <v>-6.212</v>
       </c>
       <c r="I15" t="n">
         <v>7.854399999999998</v>
@@ -1600,10 +1600,10 @@
         <v>11.5815</v>
       </c>
       <c r="K15" t="n">
-        <v>6.9307</v>
+        <v>6.930699999999998</v>
       </c>
       <c r="L15" t="n">
-        <v>4.650699999999998</v>
+        <v>4.6507</v>
       </c>
       <c r="M15" t="n">
         <v>-9.938799999999999</v>
@@ -1624,10 +1624,10 @@
         <v>19.2419</v>
       </c>
       <c r="S15" t="n">
-        <v>10.1659</v>
+        <v>11.0877</v>
       </c>
       <c r="T15" t="n">
-        <v>7.1268</v>
+        <v>8.0489</v>
       </c>
       <c r="U15" t="n">
         <v>3.039</v>
@@ -1636,7 +1636,7 @@
         <v>1.2982</v>
       </c>
       <c r="W15" t="n">
-        <v>5.795100000000001</v>
+        <v>5.7951</v>
       </c>
       <c r="X15" t="n">
         <v>-4.4969</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.9339</v>
+        <v>4.3026</v>
       </c>
       <c r="E16" t="n">
-        <v>3.7667</v>
+        <v>3.8628</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1673</v>
+        <v>0.4398</v>
       </c>
       <c r="G16" t="n">
         <v>1.7786</v>
@@ -1702,13 +1702,13 @@
         <v>1.6493</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.3945</v>
+        <v>-1.0258</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6056</v>
+        <v>-0.5094</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.7889</v>
+        <v>-0.5164</v>
       </c>
       <c r="V16" t="n">
         <v>1.9005</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. DIAGO ROS</t>
+          <t>G. GONZALEZ GARCIA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.0892</v>
+        <v>2.223</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9126</v>
+        <v>0.4331</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1767</v>
+        <v>1.7899</v>
       </c>
       <c r="G17" t="n">
-        <v>1.4913</v>
+        <v>0.5127</v>
       </c>
       <c r="H17" t="n">
-        <v>1.3761</v>
+        <v>2.7886</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1152</v>
+        <v>-2.2759</v>
       </c>
       <c r="J17" t="n">
-        <v>1.5664</v>
+        <v>1.2289</v>
       </c>
       <c r="K17" t="n">
-        <v>1.4831</v>
+        <v>3.152</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0833</v>
+        <v>-1.9231</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.0751</v>
+        <v>-0.7161</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1069</v>
+        <v>-0.3633</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0318</v>
+        <v>-0.3528</v>
       </c>
       <c r="P17" t="n">
         <v>1.2828</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2828</v>
+        <v>2.1991</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3287</v>
+        <v>-0.5175</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3462</v>
+        <v>-0.5234</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0175</v>
+        <v>0.0058</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.0136</v>
+        <v>0.945</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.6439</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0136</v>
+        <v>0.3011</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. GONZALEZ GARCIA</t>
+          <t>A. DIAGO ROS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.8078</v>
+        <v>1.1378</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2408</v>
+        <v>1.4318</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5669</v>
+        <v>-0.294</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5127</v>
+        <v>1.4913</v>
       </c>
       <c r="H18" t="n">
-        <v>2.7886</v>
+        <v>1.3761</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.2759</v>
+        <v>0.1152</v>
       </c>
       <c r="J18" t="n">
-        <v>1.2289</v>
+        <v>1.5664</v>
       </c>
       <c r="K18" t="n">
-        <v>3.152</v>
+        <v>1.4831</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.9231</v>
+        <v>0.0833</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7161</v>
+        <v>-0.0751</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3633</v>
+        <v>-0.1069</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3528</v>
+        <v>0.0318</v>
       </c>
       <c r="P18" t="n">
         <v>1.2828</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.1991</v>
+        <v>1.2828</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9328</v>
+        <v>-0.6227</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7157</v>
+        <v>-0.1346</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2171</v>
+        <v>-0.4881</v>
       </c>
       <c r="V18" t="n">
-        <v>0.945</v>
+        <v>-1.0136</v>
       </c>
       <c r="W18" t="n">
-        <v>0.6439</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.3011</v>
+        <v>-1.0136</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6141</v>
+        <v>0.9346</v>
       </c>
       <c r="E19" t="n">
-        <v>3.3831</v>
+        <v>3.5754</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.769</v>
+        <v>-2.6408</v>
       </c>
       <c r="G19" t="n">
         <v>0.9722</v>
@@ -1936,13 +1936,13 @@
         <v>0.9163</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.264</v>
+        <v>-0.9434</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3673</v>
+        <v>-0.175</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.8967000000000001</v>
+        <v>-0.7685</v>
       </c>
       <c r="V19" t="n">
         <v>-0.0104</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4221</v>
+        <v>-0.3719</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5504</v>
+        <v>-0.2188</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1283</v>
+        <v>-0.1531</v>
       </c>
       <c r="G20" t="n">
         <v>0.0547</v>
@@ -2014,13 +2014,13 @@
         <v>0.9163</v>
       </c>
       <c r="S20" t="n">
-        <v>0.9722</v>
+        <v>0.1782</v>
       </c>
       <c r="T20" t="n">
-        <v>0.9147999999999999</v>
+        <v>0.1456</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0574</v>
+        <v>0.0326</v>
       </c>
       <c r="V20" t="n">
         <v>0.3115</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.0747</v>
+        <v>-0.6828</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9609</v>
+        <v>-0.6724</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1138</v>
+        <v>-0.0103</v>
       </c>
       <c r="G21" t="n">
         <v>-0.8102</v>
@@ -2092,13 +2092,13 @@
         <v>1.2828</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6206</v>
+        <v>-0.2287</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3122</v>
+        <v>-0.0237</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3084</v>
+        <v>-0.205</v>
       </c>
       <c r="V21" t="n">
         <v>-0.0104</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.8092</v>
+        <v>-2.1298</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.4467</v>
+        <v>-2.3506</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6375999999999999</v>
+        <v>0.2208</v>
       </c>
       <c r="G22" t="n">
         <v>1.0544</v>
@@ -2170,13 +2170,13 @@
         <v>1.2828</v>
       </c>
       <c r="S22" t="n">
-        <v>0.7754</v>
+        <v>0.4547</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3303</v>
+        <v>-0.2342</v>
       </c>
       <c r="U22" t="n">
-        <v>1.1057</v>
+        <v>0.6889</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2566</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.2459</v>
+        <v>-2.5125</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.9663</v>
+        <v>-2.1586</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2796</v>
+        <v>-0.3539</v>
       </c>
       <c r="G23" t="n">
         <v>0.6492</v>
@@ -2248,13 +2248,13 @@
         <v>1.0995</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8369</v>
+        <v>-1.1035</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0015</v>
+        <v>-0.1938</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8354</v>
+        <v>-0.9097</v>
       </c>
       <c r="V23" t="n">
         <v>-1.3251</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>G. BORREGA BERTOLIN</t>
+          <t>P. PAREJA ANDRES</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.8739</v>
+        <v>-2.8463</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.7457</v>
+        <v>-0.6593</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.1282</v>
+        <v>-2.187</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.2745</v>
+        <v>-1.1966</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.2553</v>
+        <v>-0.7604</v>
       </c>
       <c r="I24" t="n">
-        <v>0.9808</v>
+        <v>-0.4361</v>
       </c>
       <c r="J24" t="n">
-        <v>1.286</v>
+        <v>0.3226</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.0157</v>
+        <v>0.2135</v>
       </c>
       <c r="L24" t="n">
-        <v>1.3018</v>
+        <v>0.1091</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.5605</v>
+        <v>-1.5192</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.2395</v>
+        <v>-0.9739</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.321</v>
+        <v>-0.5452</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.3823</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q24" t="n">
-        <v>-4.5814</v>
+        <v>-0.9163</v>
       </c>
       <c r="R24" t="n">
-        <v>2.1991</v>
+        <v>0.733</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.4259</v>
+        <v>-1.076</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0392</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.3867</v>
+        <v>-1.0104</v>
       </c>
       <c r="V24" t="n">
-        <v>1.2088</v>
+        <v>-0.3905</v>
       </c>
       <c r="W24" t="n">
-        <v>1.5889</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.3801</v>
+        <v>-0.3905</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>P. PAREJA ANDRES</t>
+          <t>G. BORREGA BERTOLIN</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.6258</v>
+        <v>-3.1565</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.2362</v>
+        <v>-2.2265</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.3895</v>
+        <v>-0.9301</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.1966</v>
+        <v>-0.2745</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.7604</v>
+        <v>-1.2553</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.4361</v>
+        <v>0.9808</v>
       </c>
       <c r="J25" t="n">
-        <v>0.3226</v>
+        <v>1.286</v>
       </c>
       <c r="K25" t="n">
-        <v>0.2135</v>
+        <v>-0.0157</v>
       </c>
       <c r="L25" t="n">
-        <v>0.1091</v>
+        <v>1.3018</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.5192</v>
+        <v>-1.5605</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.9739</v>
+        <v>-1.2395</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.5452</v>
+        <v>-0.321</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.1833</v>
+        <v>-2.3823</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.9163</v>
+        <v>-4.5814</v>
       </c>
       <c r="R25" t="n">
-        <v>0.733</v>
+        <v>2.1991</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.8554</v>
+        <v>-1.7085</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6425</v>
+        <v>-0.52</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.2129</v>
+        <v>-1.1886</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.3905</v>
+        <v>1.2088</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.5889</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.3905</v>
+        <v>-0.3801</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.6338</v>
+        <v>-5.0787</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.3363</v>
+        <v>-2.8555</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.2975</v>
+        <v>-2.2232</v>
       </c>
       <c r="G26" t="n">
         <v>-2.0055</v>
@@ -2482,13 +2482,13 @@
         <v>2.0158</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.6179</v>
+        <v>-1.0628</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.9909</v>
+        <v>-0.5102</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.6269</v>
+        <v>-0.5526</v>
       </c>
       <c r="V26" t="n">
         <v>-1.2774</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-7.4594</v>
+        <v>-7.034</v>
       </c>
       <c r="E27" t="n">
         <v>-5.6952</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.7643</v>
+        <v>-1.3388</v>
       </c>
       <c r="G27" t="n">
         <v>-3.8688</v>
@@ -2560,13 +2560,13 @@
         <v>0.9163</v>
       </c>
       <c r="S27" t="n">
-        <v>-2.2943</v>
+        <v>-1.8688</v>
       </c>
       <c r="T27" t="n">
         <v>-0.2949</v>
       </c>
       <c r="U27" t="n">
-        <v>-1.9994</v>
+        <v>-1.5739</v>
       </c>
       <c r="V27" t="n">
         <v>-0.3801</v>
@@ -2593,19 +2593,19 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-15.8556</v>
+        <v>-15.2145</v>
       </c>
       <c r="E28" t="n">
-        <v>-7.5337</v>
+        <v>-7.533799999999999</v>
       </c>
       <c r="F28" t="n">
-        <v>-8.3217</v>
+        <v>-7.680699999999999</v>
       </c>
       <c r="G28" t="n">
         <v>-1.6425</v>
       </c>
       <c r="H28" t="n">
-        <v>6.211900000000001</v>
+        <v>6.2119</v>
       </c>
       <c r="I28" t="n">
         <v>-7.8544</v>
@@ -2638,13 +2638,13 @@
         <v>16.4931</v>
       </c>
       <c r="S28" t="n">
-        <v>-10.166</v>
+        <v>-9.524800000000001</v>
       </c>
       <c r="T28" t="n">
-        <v>-3.0391</v>
+        <v>-3.0392</v>
       </c>
       <c r="U28" t="n">
-        <v>-7.126800000000001</v>
+        <v>-6.4859</v>
       </c>
       <c r="V28" t="n">
         <v>-1.2983</v>
@@ -2653,7 +2653,7 @@
         <v>4.8084</v>
       </c>
       <c r="X28" t="n">
-        <v>-6.1066</v>
+        <v>-6.106599999999999</v>
       </c>
     </row>
   </sheetData>
